--- a/src/source/table3.xlsx
+++ b/src/source/table3.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
     <t>鸠江区三线水位测站记录情况登记表</t>
   </si>
   <si>
-    <t xml:space="preserve">填报日期：                                      </t>
+    <t>填报日期：</t>
   </si>
   <si>
     <t>序号</t>
@@ -154,22 +154,24 @@
   </si>
   <si>
     <t>备注：1、数据来源为查询安徽水信息网所得；
-     2、浅蓝色为超设防水位，深蓝色为超警戒水位，红色为超保证水位。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
+     2、浅蓝色为超设防水位，深蓝色为超警戒水位，红色为超保证水位；
+     3、近期每三日发布一次，达设防水位每日发布一次，并视水情动态调整发布频次。</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="\+0.00;\-0.00"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -577,7 +579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -595,7 +597,9 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -607,21 +611,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -784,234 +773,227 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1336,359 +1318,352 @@
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.75454545454545" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.6272727272727" style="2" customWidth="1"/>
-    <col min="4" max="7" width="11.8727272727273" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.2545454545455" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="3.75454545454545" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="15.6272727272727" customWidth="1"/>
+    <col min="4" max="7" width="11.8727272727273" customWidth="1"/>
+    <col min="8" max="9" width="11.2545454545455" customWidth="1"/>
+    <col min="10" max="16383" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:9">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="1" ht="14.25" customHeight="1" spans="1:9">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="20" customHeight="1" spans="1:9">
-      <c r="A3" s="8" t="s">
+    <row r="3" s="2" customFormat="1" ht="16" customHeight="1" spans="1:9">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="10"/>
+      <c r="I3" s="24"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="20" customHeight="1" spans="1:9">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12" t="s">
+    <row r="4" s="2" customFormat="1" ht="16" customHeight="1" spans="1:9">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A5" s="14">
+    <row r="5" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18">
-        <f>D5-E5</f>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15">
+        <f t="shared" ref="F5:F14" si="0">D5-E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19">
+      <c r="G5" s="16"/>
+      <c r="H5" s="17">
         <v>44025</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="25">
         <v>15.21</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A6" s="20">
+    <row r="6" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18">
-        <f t="shared" ref="F6:F14" si="0">D6-E6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19">
-        <v>44033</v>
-      </c>
-      <c r="I6" s="26">
-        <v>12.76</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A7" s="20">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19">
+      <c r="G6" s="16"/>
+      <c r="H6" s="17">
         <v>44033</v>
       </c>
-      <c r="I7" s="27">
-        <v>12.72</v>
+      <c r="I6" s="25">
+        <v>12.76</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A8" s="20">
-        <v>4</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18">
+    <row r="7" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A7" s="18">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19">
-        <v>44029</v>
-      </c>
-      <c r="I8" s="26">
-        <v>13.19</v>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17">
+        <v>44033</v>
+      </c>
+      <c r="I7" s="26">
+        <v>12.72</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A9" s="20">
-        <v>5</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18">
+    <row r="8" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A8" s="18">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19">
-        <v>44033</v>
-      </c>
-      <c r="I9" s="27">
-        <v>12.72</v>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17">
+        <v>44029</v>
+      </c>
+      <c r="I8" s="25">
+        <v>13.19</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A10" s="20">
-        <v>6</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18">
+    <row r="9" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A9" s="18">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19">
+      <c r="G9" s="16"/>
+      <c r="H9" s="17">
         <v>44033</v>
       </c>
-      <c r="I10" s="27">
-        <v>12.77</v>
+      <c r="I9" s="26">
+        <v>12.72</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A11" s="20">
-        <v>7</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18">
+    <row r="10" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A10" s="18">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19">
-        <v>44030</v>
-      </c>
-      <c r="I11" s="27">
-        <v>12.1</v>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17">
+        <v>44033</v>
+      </c>
+      <c r="I10" s="26">
+        <v>12.77</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A12" s="20">
-        <v>8</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18">
+    <row r="11" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A11" s="18">
+        <v>7</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19">
-        <v>44025</v>
-      </c>
-      <c r="I12" s="27">
-        <v>15.21</v>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17">
+        <v>44030</v>
+      </c>
+      <c r="I11" s="26">
+        <v>12.1</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A13" s="20">
-        <v>9</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="22" t="s">
+    <row r="12" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A12" s="18">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19">
+      <c r="G12" s="16"/>
+      <c r="H12" s="17">
         <v>44025</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I12" s="26">
         <v>15.21</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A14" s="23">
-        <v>10</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18">
+    <row r="13" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A13" s="18">
+        <v>9</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19">
+      <c r="G13" s="16"/>
+      <c r="H13" s="17">
         <v>44025</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I13" s="26">
         <v>15.21</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A15" s="24" t="s">
+    <row r="14" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A14" s="21">
+        <v>10</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17">
+        <v>44025</v>
+      </c>
+      <c r="I14" s="26">
+        <v>15.21</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="48" customHeight="1" spans="1:9">
+      <c r="A15" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:9">
-      <c r="A16" s="25" t="s">
+    <row r="16" customFormat="1" spans="1:1">
+      <c r="A16" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A16:I16"/>
@@ -1696,7 +1671,8 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.751388888888889" right="0.751388888888889" top="1" bottom="0.802777777777778" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/src/source/table3.xlsx
+++ b/src/source/table3.xlsx
@@ -1319,7 +1319,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.75454545454545" customWidth="1"/>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="15.6272727272727" customWidth="1"/>
     <col min="4" max="7" width="11.8727272727273" customWidth="1"/>
     <col min="8" max="9" width="11.2545454545455" customWidth="1"/>
@@ -1402,7 +1402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="5" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="6" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A6" s="18">
         <v>2</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>12.76</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="7" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A7" s="18">
         <v>3</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>12.72</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="8" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A8" s="18">
         <v>4</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>13.19</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="9" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A9" s="18">
         <v>5</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>12.72</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="10" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A10" s="18">
         <v>6</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="11" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A11" s="18">
         <v>7</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="12" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A12" s="18">
         <v>8</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="13" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A13" s="18">
         <v>9</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="14" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A14" s="21">
         <v>10</v>
       </c>
